--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085285D3-0F29-425B-AF55-08523884D48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757F3D22-E3BB-4D27-8561-4D05F0B5F506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="238">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -792,15 +792,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10,53</t>
+    <t>12,30,55,80,133,155,175,205,238</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>40,72,144,175,205,238</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>55,80,144,175,205,238</t>
+    <t>14,25,46,68,87</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1344,7 +1340,7 @@
         <v>43400002</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -1397,7 +1393,7 @@
         <v>43400002</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -1450,7 +1446,7 @@
         <v>43400002</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -1503,7 +1499,7 @@
         <v>43400002</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757F3D22-E3BB-4D27-8561-4D05F0B5F506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3C8C77-A754-47AB-9778-B50A5E94B890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14,25,46,68,87</t>
+    <t>11,44,65,83,109</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3C8C77-A754-47AB-9778-B50A5E94B890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A7C9E9-F33B-46CF-AD6D-A562578AAA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11,44,65,83,109</t>
+    <t>11,38,59</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A7C9E9-F33B-46CF-AD6D-A562578AAA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB740E99-425B-4B61-8EB8-467DE074732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11,38,59</t>
+    <t>11,38,56</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB740E99-425B-4B61-8EB8-467DE074732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6889DA-E614-4983-A038-DB07C2BA2517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="241">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -797,6 +797,18 @@
   </si>
   <si>
     <t>11,38,56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1133,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q164"/>
+  <dimension ref="A1:R164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1150,15 +1162,16 @@
     <col min="14" max="14" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="7.125" style="1"/>
+    <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1210,8 +1223,11 @@
       <c r="Q2" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R2" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1263,8 +1279,11 @@
       <c r="Q3" s="1" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R3" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1335,11 @@
       <c r="Q4" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R4" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1369,8 +1391,11 @@
       <c r="Q5" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R5" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1422,8 +1447,11 @@
       <c r="Q6" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R6" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1475,8 +1503,11 @@
       <c r="Q7" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R7" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1528,8 +1559,11 @@
       <c r="Q8" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R8" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1581,8 +1615,11 @@
       <c r="Q9" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R9" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1634,8 +1671,11 @@
       <c r="Q10" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R10" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1687,8 +1727,11 @@
       <c r="Q11" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R11" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1740,8 +1783,11 @@
       <c r="Q12" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R12" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1793,8 +1839,11 @@
       <c r="Q13" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R13" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1846,8 +1895,11 @@
       <c r="Q14" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R14" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1899,8 +1951,11 @@
       <c r="Q15" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R15" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1952,8 +2007,11 @@
       <c r="Q16" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R16" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -2005,8 +2063,11 @@
       <c r="Q17" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R17" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -2058,8 +2119,11 @@
       <c r="Q18" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R18" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2111,8 +2175,11 @@
       <c r="Q19" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R19" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2164,8 +2231,11 @@
       <c r="Q20" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R20" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2217,8 +2287,11 @@
       <c r="Q21" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R21" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2270,8 +2343,11 @@
       <c r="Q22" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R22" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2323,8 +2399,11 @@
       <c r="Q23" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R23" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2376,8 +2455,11 @@
       <c r="Q24" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R24" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2429,8 +2511,11 @@
       <c r="Q25" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R25" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2482,8 +2567,11 @@
       <c r="Q26" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R26" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2535,8 +2623,11 @@
       <c r="Q27" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R27" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2588,8 +2679,11 @@
       <c r="Q28" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R28" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -2641,8 +2735,11 @@
       <c r="Q29" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R29" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2694,8 +2791,11 @@
       <c r="Q30" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R30" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -2747,8 +2847,11 @@
       <c r="Q31" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R31" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -2800,8 +2903,11 @@
       <c r="Q32" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R32" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2853,8 +2959,11 @@
       <c r="Q33" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R33" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -2906,8 +3015,11 @@
       <c r="Q34" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R34" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -2959,8 +3071,11 @@
       <c r="Q35" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R35" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -3012,8 +3127,11 @@
       <c r="Q36" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R36" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -3065,8 +3183,11 @@
       <c r="Q37" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R37" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -3118,8 +3239,11 @@
       <c r="Q38" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R38" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -3171,8 +3295,11 @@
       <c r="Q39" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R39" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -3224,8 +3351,11 @@
       <c r="Q40" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R40" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -3277,8 +3407,11 @@
       <c r="Q41" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R41" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -3330,8 +3463,11 @@
       <c r="Q42" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R42" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -3383,8 +3519,11 @@
       <c r="Q43" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R43" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -3436,8 +3575,11 @@
       <c r="Q44" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R44" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -3489,8 +3631,11 @@
       <c r="Q45" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R45" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -3542,8 +3687,11 @@
       <c r="Q46" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R46" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -3595,8 +3743,11 @@
       <c r="Q47" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R47" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -3648,8 +3799,11 @@
       <c r="Q48" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R48" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -3701,8 +3855,11 @@
       <c r="Q49" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R49" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -3754,8 +3911,11 @@
       <c r="Q50" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R50" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -3807,8 +3967,11 @@
       <c r="Q51" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R51" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -3860,8 +4023,11 @@
       <c r="Q52" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R52" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -3913,8 +4079,11 @@
       <c r="Q53" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R53" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -3966,8 +4135,11 @@
       <c r="Q54" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R54" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -4019,8 +4191,11 @@
       <c r="Q55" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R55" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -4072,8 +4247,11 @@
       <c r="Q56" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R56" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -4125,8 +4303,11 @@
       <c r="Q57" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R57" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -4178,8 +4359,11 @@
       <c r="Q58" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R58" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -4231,8 +4415,11 @@
       <c r="Q59" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R59" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -4284,8 +4471,11 @@
       <c r="Q60" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R60" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -4337,8 +4527,11 @@
       <c r="Q61" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R61" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -4390,8 +4583,11 @@
       <c r="Q62" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R62" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -4443,8 +4639,11 @@
       <c r="Q63" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R63" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -4496,8 +4695,11 @@
       <c r="Q64" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R64" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -4549,8 +4751,11 @@
       <c r="Q65" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R65" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -4602,8 +4807,11 @@
       <c r="Q66" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R66" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -4655,8 +4863,11 @@
       <c r="Q67" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R67" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -4708,8 +4919,11 @@
       <c r="Q68" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R68" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -4761,8 +4975,11 @@
       <c r="Q69" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R69" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -4814,8 +5031,11 @@
       <c r="Q70" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R70" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -4867,8 +5087,11 @@
       <c r="Q71" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R71" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -4920,8 +5143,11 @@
       <c r="Q72" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R72" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -4973,8 +5199,11 @@
       <c r="Q73" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R73" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -5026,8 +5255,11 @@
       <c r="Q74" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R74" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -5079,8 +5311,11 @@
       <c r="Q75" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R75" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -5132,8 +5367,11 @@
       <c r="Q76" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R76" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -5185,8 +5423,11 @@
       <c r="Q77" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R77" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -5238,8 +5479,11 @@
       <c r="Q78" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R78" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -5291,8 +5535,11 @@
       <c r="Q79" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R79" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -5344,8 +5591,11 @@
       <c r="Q80" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R80" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -5397,8 +5647,11 @@
       <c r="Q81" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R81" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -5450,8 +5703,11 @@
       <c r="Q82" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R82" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -5503,8 +5759,11 @@
       <c r="Q83" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R83" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -5556,8 +5815,11 @@
       <c r="Q84" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R84" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -5609,8 +5871,11 @@
       <c r="Q85" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R85" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -5662,8 +5927,11 @@
       <c r="Q86" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R86" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -5715,8 +5983,11 @@
       <c r="Q87" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R87" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -5768,8 +6039,11 @@
       <c r="Q88" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R88" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -5821,8 +6095,11 @@
       <c r="Q89" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R89" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -5874,8 +6151,11 @@
       <c r="Q90" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R90" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -5927,8 +6207,11 @@
       <c r="Q91" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R91" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -5980,8 +6263,11 @@
       <c r="Q92" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R92" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -6033,8 +6319,11 @@
       <c r="Q93" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R93" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -6086,8 +6375,11 @@
       <c r="Q94" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R94" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -6139,8 +6431,11 @@
       <c r="Q95" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R95" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -6192,8 +6487,11 @@
       <c r="Q96" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R96" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -6245,8 +6543,11 @@
       <c r="Q97" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R97" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -6298,8 +6599,11 @@
       <c r="Q98" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R98" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -6351,8 +6655,11 @@
       <c r="Q99" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R99" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -6404,8 +6711,11 @@
       <c r="Q100" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R100" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -6457,8 +6767,11 @@
       <c r="Q101" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R101" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -6510,8 +6823,11 @@
       <c r="Q102" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R102" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -6563,8 +6879,11 @@
       <c r="Q103" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R103" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -6616,8 +6935,11 @@
       <c r="Q104" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R104" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>101</v>
       </c>
@@ -6669,8 +6991,11 @@
       <c r="Q105" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R105" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>102</v>
       </c>
@@ -6722,8 +7047,11 @@
       <c r="Q106" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R106" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>103</v>
       </c>
@@ -6775,8 +7103,11 @@
       <c r="Q107" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R107" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>104</v>
       </c>
@@ -6828,8 +7159,11 @@
       <c r="Q108" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R108" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>105</v>
       </c>
@@ -6881,8 +7215,11 @@
       <c r="Q109" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R109" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>106</v>
       </c>
@@ -6934,8 +7271,11 @@
       <c r="Q110" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R110" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>107</v>
       </c>
@@ -6987,8 +7327,11 @@
       <c r="Q111" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R111" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>108</v>
       </c>
@@ -7040,8 +7383,11 @@
       <c r="Q112" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R112" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>109</v>
       </c>
@@ -7093,8 +7439,11 @@
       <c r="Q113" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R113" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>110</v>
       </c>
@@ -7146,8 +7495,11 @@
       <c r="Q114" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R114" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>111</v>
       </c>
@@ -7199,8 +7551,11 @@
       <c r="Q115" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R115" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>112</v>
       </c>
@@ -7252,8 +7607,11 @@
       <c r="Q116" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R116" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>113</v>
       </c>
@@ -7305,8 +7663,11 @@
       <c r="Q117" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R117" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>114</v>
       </c>
@@ -7358,8 +7719,11 @@
       <c r="Q118" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R118" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>115</v>
       </c>
@@ -7411,8 +7775,11 @@
       <c r="Q119" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R119" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>116</v>
       </c>
@@ -7464,8 +7831,11 @@
       <c r="Q120" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R120" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>117</v>
       </c>
@@ -7517,8 +7887,11 @@
       <c r="Q121" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R121" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>118</v>
       </c>
@@ -7570,8 +7943,11 @@
       <c r="Q122" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R122" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>119</v>
       </c>
@@ -7623,8 +7999,11 @@
       <c r="Q123" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R123" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>120</v>
       </c>
@@ -7676,8 +8055,11 @@
       <c r="Q124" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R124" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>121</v>
       </c>
@@ -7729,8 +8111,11 @@
       <c r="Q125" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R125" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>122</v>
       </c>
@@ -7782,8 +8167,11 @@
       <c r="Q126" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R126" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>123</v>
       </c>
@@ -7835,8 +8223,11 @@
       <c r="Q127" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R127" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>124</v>
       </c>
@@ -7888,8 +8279,11 @@
       <c r="Q128" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R128" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>125</v>
       </c>
@@ -7941,8 +8335,11 @@
       <c r="Q129" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R129" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>126</v>
       </c>
@@ -7994,8 +8391,11 @@
       <c r="Q130" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R130" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>127</v>
       </c>
@@ -8047,8 +8447,11 @@
       <c r="Q131" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R131" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>128</v>
       </c>
@@ -8100,8 +8503,11 @@
       <c r="Q132" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R132" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>129</v>
       </c>
@@ -8153,8 +8559,11 @@
       <c r="Q133" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R133" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>130</v>
       </c>
@@ -8206,8 +8615,11 @@
       <c r="Q134" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R134" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -8259,8 +8671,11 @@
       <c r="Q135" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R135" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>132</v>
       </c>
@@ -8312,8 +8727,11 @@
       <c r="Q136" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R136" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>133</v>
       </c>
@@ -8365,8 +8783,11 @@
       <c r="Q137" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R137" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>134</v>
       </c>
@@ -8418,8 +8839,11 @@
       <c r="Q138" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R138" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>135</v>
       </c>
@@ -8471,8 +8895,11 @@
       <c r="Q139" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R139" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>136</v>
       </c>
@@ -8524,8 +8951,11 @@
       <c r="Q140" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R140" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>137</v>
       </c>
@@ -8577,8 +9007,11 @@
       <c r="Q141" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R141" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>138</v>
       </c>
@@ -8630,8 +9063,11 @@
       <c r="Q142" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R142" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>139</v>
       </c>
@@ -8683,8 +9119,11 @@
       <c r="Q143" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R143" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>140</v>
       </c>
@@ -8736,8 +9175,11 @@
       <c r="Q144" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R144" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>141</v>
       </c>
@@ -8789,8 +9231,11 @@
       <c r="Q145" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R145" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>142</v>
       </c>
@@ -8842,8 +9287,11 @@
       <c r="Q146" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R146" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>143</v>
       </c>
@@ -8895,8 +9343,11 @@
       <c r="Q147" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R147" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>144</v>
       </c>
@@ -8948,8 +9399,11 @@
       <c r="Q148" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R148" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>145</v>
       </c>
@@ -9001,8 +9455,11 @@
       <c r="Q149" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R149" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>146</v>
       </c>
@@ -9054,8 +9511,11 @@
       <c r="Q150" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R150" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>147</v>
       </c>
@@ -9107,8 +9567,11 @@
       <c r="Q151" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R151" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>148</v>
       </c>
@@ -9160,8 +9623,11 @@
       <c r="Q152" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R152" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>149</v>
       </c>
@@ -9213,8 +9679,11 @@
       <c r="Q153" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R153" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>150</v>
       </c>
@@ -9266,8 +9735,11 @@
       <c r="Q154" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R154" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>151</v>
       </c>
@@ -9319,8 +9791,11 @@
       <c r="Q155" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R155" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>152</v>
       </c>
@@ -9372,8 +9847,11 @@
       <c r="Q156" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R156" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>153</v>
       </c>
@@ -9425,8 +9903,11 @@
       <c r="Q157" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R157" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>154</v>
       </c>
@@ -9478,8 +9959,11 @@
       <c r="Q158" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R158" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>155</v>
       </c>
@@ -9531,8 +10015,11 @@
       <c r="Q159" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R159" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>156</v>
       </c>
@@ -9584,8 +10071,11 @@
       <c r="Q160" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R160" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>157</v>
       </c>
@@ -9637,8 +10127,11 @@
       <c r="Q161" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R161" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>158</v>
       </c>
@@ -9690,8 +10183,11 @@
       <c r="Q162" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R162" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>159</v>
       </c>
@@ -9743,8 +10239,11 @@
       <c r="Q163" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R163" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>160</v>
       </c>
@@ -9795,6 +10294,9 @@
       </c>
       <c r="Q164" s="3" t="s">
         <v>231</v>
+      </c>
+      <c r="R164" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6889DA-E614-4983-A038-DB07C2BA2517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112CD598-6637-4295-9718-EAB4CDF6D0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -1224,7 +1224,7 @@
         <v>227</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112CD598-6637-4295-9718-EAB4CDF6D0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3667EB-B836-492B-B537-FB4460A8D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="240">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -785,10 +785,6 @@
   </si>
   <si>
     <t>18,78,150,210,320,440,580</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18,78,150,210,320,440,580,740,920</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1280,7 +1276,7 @@
         <v>225</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
@@ -1336,7 +1332,7 @@
         <v>226</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
@@ -1362,7 +1358,7 @@
         <v>43400002</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -1392,7 +1388,7 @@
         <v>231</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
@@ -1418,7 +1414,7 @@
         <v>43400002</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -1448,7 +1444,7 @@
         <v>231</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -1474,7 +1470,7 @@
         <v>43400002</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -1504,7 +1500,7 @@
         <v>231</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
@@ -1530,7 +1526,7 @@
         <v>43400002</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -1560,7 +1556,7 @@
         <v>231</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
@@ -1616,7 +1612,7 @@
         <v>231</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.15">
@@ -1672,7 +1668,7 @@
         <v>231</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
@@ -1697,8 +1693,8 @@
       <c r="G11" s="1">
         <v>43400002</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>235</v>
+      <c r="H11" s="1">
+        <v>0</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
@@ -1719,7 +1715,7 @@
         <v>700</v>
       </c>
       <c r="O11" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P11" s="1">
         <v>1003</v>
@@ -1727,8 +1723,8 @@
       <c r="Q11" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R11" s="1" t="s">
-        <v>240</v>
+      <c r="R11" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
@@ -1784,7 +1780,7 @@
         <v>231</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.15">
@@ -1840,7 +1836,7 @@
         <v>231</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1896,7 +1892,7 @@
         <v>231</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.15">
@@ -1952,7 +1948,7 @@
         <v>231</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.15">
@@ -2008,7 +2004,7 @@
         <v>231</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">
@@ -2064,7 +2060,7 @@
         <v>231</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.15">
@@ -2120,7 +2116,7 @@
         <v>231</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.15">
@@ -2176,7 +2172,7 @@
         <v>231</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.15">
@@ -2232,7 +2228,7 @@
         <v>231</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.15">
@@ -2288,7 +2284,7 @@
         <v>231</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
@@ -2344,7 +2340,7 @@
         <v>231</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
@@ -2400,7 +2396,7 @@
         <v>231</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
@@ -2456,7 +2452,7 @@
         <v>231</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
@@ -2512,7 +2508,7 @@
         <v>231</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.15">
@@ -2568,7 +2564,7 @@
         <v>231</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.15">
@@ -2624,7 +2620,7 @@
         <v>231</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.15">
@@ -2680,7 +2676,7 @@
         <v>231</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.15">
@@ -2736,7 +2732,7 @@
         <v>231</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.15">
@@ -2792,7 +2788,7 @@
         <v>231</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.15">
@@ -2848,7 +2844,7 @@
         <v>231</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.15">
@@ -2904,7 +2900,7 @@
         <v>231</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.15">
@@ -2960,7 +2956,7 @@
         <v>231</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.15">
@@ -3016,7 +3012,7 @@
         <v>231</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.15">
@@ -3072,7 +3068,7 @@
         <v>231</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.15">
@@ -3128,7 +3124,7 @@
         <v>231</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.15">
@@ -3184,7 +3180,7 @@
         <v>231</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.15">
@@ -3240,7 +3236,7 @@
         <v>231</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.15">
@@ -3296,7 +3292,7 @@
         <v>231</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.15">
@@ -3352,7 +3348,7 @@
         <v>231</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.15">
@@ -3408,7 +3404,7 @@
         <v>231</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.15">
@@ -3464,7 +3460,7 @@
         <v>231</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.15">
@@ -3520,7 +3516,7 @@
         <v>231</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.15">
@@ -3576,7 +3572,7 @@
         <v>231</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.15">
@@ -3632,7 +3628,7 @@
         <v>231</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.15">
@@ -3688,7 +3684,7 @@
         <v>231</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.15">
@@ -3744,7 +3740,7 @@
         <v>231</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.15">
@@ -3800,7 +3796,7 @@
         <v>231</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.15">
@@ -3856,7 +3852,7 @@
         <v>231</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.15">
@@ -3912,7 +3908,7 @@
         <v>231</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.15">
@@ -3968,7 +3964,7 @@
         <v>231</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.15">
@@ -4024,7 +4020,7 @@
         <v>231</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.15">
@@ -4080,7 +4076,7 @@
         <v>231</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.15">
@@ -4136,7 +4132,7 @@
         <v>231</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.15">
@@ -4192,7 +4188,7 @@
         <v>231</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.15">
@@ -4248,7 +4244,7 @@
         <v>231</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.15">
@@ -4304,7 +4300,7 @@
         <v>231</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.15">
@@ -4360,7 +4356,7 @@
         <v>231</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.15">
@@ -4416,7 +4412,7 @@
         <v>231</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.15">
@@ -4472,7 +4468,7 @@
         <v>231</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.15">
@@ -4528,7 +4524,7 @@
         <v>231</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.15">
@@ -4584,7 +4580,7 @@
         <v>231</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.15">
@@ -4640,7 +4636,7 @@
         <v>231</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.15">
@@ -4696,7 +4692,7 @@
         <v>231</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.15">
@@ -4752,7 +4748,7 @@
         <v>231</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.15">
@@ -4808,7 +4804,7 @@
         <v>231</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.15">
@@ -4864,7 +4860,7 @@
         <v>231</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.15">
@@ -4920,7 +4916,7 @@
         <v>231</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.15">
@@ -4976,7 +4972,7 @@
         <v>231</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.15">
@@ -5032,7 +5028,7 @@
         <v>231</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.15">
@@ -5088,7 +5084,7 @@
         <v>231</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.15">
@@ -5144,7 +5140,7 @@
         <v>231</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.15">
@@ -5200,7 +5196,7 @@
         <v>231</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.15">
@@ -5256,7 +5252,7 @@
         <v>231</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.15">
@@ -5312,7 +5308,7 @@
         <v>231</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.15">
@@ -5368,7 +5364,7 @@
         <v>231</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.15">
@@ -5424,7 +5420,7 @@
         <v>231</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.15">
@@ -5480,7 +5476,7 @@
         <v>231</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.15">
@@ -5536,7 +5532,7 @@
         <v>231</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.15">
@@ -5592,7 +5588,7 @@
         <v>231</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.15">
@@ -5648,7 +5644,7 @@
         <v>231</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.15">
@@ -5704,7 +5700,7 @@
         <v>231</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.15">
@@ -5760,7 +5756,7 @@
         <v>231</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.15">
@@ -5816,7 +5812,7 @@
         <v>231</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.15">
@@ -5872,7 +5868,7 @@
         <v>231</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.15">
@@ -5928,7 +5924,7 @@
         <v>231</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.15">
@@ -5984,7 +5980,7 @@
         <v>231</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.15">
@@ -6040,7 +6036,7 @@
         <v>231</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.15">
@@ -6096,7 +6092,7 @@
         <v>231</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.15">
@@ -6152,7 +6148,7 @@
         <v>231</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.15">
@@ -6208,7 +6204,7 @@
         <v>231</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.15">
@@ -6264,7 +6260,7 @@
         <v>231</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.15">
@@ -6320,7 +6316,7 @@
         <v>231</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.15">
@@ -6376,7 +6372,7 @@
         <v>231</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.15">
@@ -6432,7 +6428,7 @@
         <v>231</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.15">
@@ -6488,7 +6484,7 @@
         <v>231</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.15">
@@ -6544,7 +6540,7 @@
         <v>231</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.15">
@@ -6600,7 +6596,7 @@
         <v>231</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.15">
@@ -6656,7 +6652,7 @@
         <v>231</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.15">
@@ -6712,7 +6708,7 @@
         <v>231</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.15">
@@ -6768,7 +6764,7 @@
         <v>231</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.15">
@@ -6824,7 +6820,7 @@
         <v>231</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.15">
@@ -6880,7 +6876,7 @@
         <v>231</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.15">
@@ -6936,7 +6932,7 @@
         <v>231</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.15">
@@ -6992,7 +6988,7 @@
         <v>231</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.15">
@@ -7048,7 +7044,7 @@
         <v>231</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.15">
@@ -7104,7 +7100,7 @@
         <v>231</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.15">
@@ -7160,7 +7156,7 @@
         <v>231</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.15">
@@ -7216,7 +7212,7 @@
         <v>231</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.15">
@@ -7272,7 +7268,7 @@
         <v>231</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.15">
@@ -7328,7 +7324,7 @@
         <v>231</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.15">
@@ -7384,7 +7380,7 @@
         <v>231</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.15">
@@ -7440,7 +7436,7 @@
         <v>231</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.15">
@@ -7496,7 +7492,7 @@
         <v>231</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.15">
@@ -7552,7 +7548,7 @@
         <v>231</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.15">
@@ -7608,7 +7604,7 @@
         <v>231</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.15">
@@ -7664,7 +7660,7 @@
         <v>231</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.15">
@@ -7720,7 +7716,7 @@
         <v>231</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.15">
@@ -7776,7 +7772,7 @@
         <v>231</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.15">
@@ -7832,7 +7828,7 @@
         <v>231</v>
       </c>
       <c r="R120" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.15">
@@ -7888,7 +7884,7 @@
         <v>231</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.15">
@@ -7944,7 +7940,7 @@
         <v>231</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.15">
@@ -8000,7 +7996,7 @@
         <v>231</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.15">
@@ -8056,7 +8052,7 @@
         <v>231</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.15">
@@ -8112,7 +8108,7 @@
         <v>231</v>
       </c>
       <c r="R125" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.15">
@@ -8168,7 +8164,7 @@
         <v>231</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.15">
@@ -8224,7 +8220,7 @@
         <v>231</v>
       </c>
       <c r="R127" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.15">
@@ -8280,7 +8276,7 @@
         <v>231</v>
       </c>
       <c r="R128" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.15">
@@ -8336,7 +8332,7 @@
         <v>231</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.15">
@@ -8392,7 +8388,7 @@
         <v>231</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.15">
@@ -8448,7 +8444,7 @@
         <v>231</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.15">
@@ -8504,7 +8500,7 @@
         <v>231</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.15">
@@ -8560,7 +8556,7 @@
         <v>231</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.15">
@@ -8616,7 +8612,7 @@
         <v>231</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.15">
@@ -8672,7 +8668,7 @@
         <v>231</v>
       </c>
       <c r="R135" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.15">
@@ -8728,7 +8724,7 @@
         <v>231</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.15">
@@ -8784,7 +8780,7 @@
         <v>231</v>
       </c>
       <c r="R137" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.15">
@@ -8840,7 +8836,7 @@
         <v>231</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.15">
@@ -8896,7 +8892,7 @@
         <v>231</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.15">
@@ -8952,7 +8948,7 @@
         <v>231</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.15">
@@ -9008,7 +9004,7 @@
         <v>231</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.15">
@@ -9064,7 +9060,7 @@
         <v>231</v>
       </c>
       <c r="R142" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.15">
@@ -9120,7 +9116,7 @@
         <v>231</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.15">
@@ -9176,7 +9172,7 @@
         <v>231</v>
       </c>
       <c r="R144" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.15">
@@ -9232,7 +9228,7 @@
         <v>231</v>
       </c>
       <c r="R145" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.15">
@@ -9288,7 +9284,7 @@
         <v>231</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.15">
@@ -9344,7 +9340,7 @@
         <v>231</v>
       </c>
       <c r="R147" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.15">
@@ -9400,7 +9396,7 @@
         <v>231</v>
       </c>
       <c r="R148" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.15">
@@ -9456,7 +9452,7 @@
         <v>231</v>
       </c>
       <c r="R149" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.15">
@@ -9512,7 +9508,7 @@
         <v>231</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.15">
@@ -9568,7 +9564,7 @@
         <v>231</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.15">
@@ -9624,7 +9620,7 @@
         <v>231</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.15">
@@ -9680,7 +9676,7 @@
         <v>231</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.15">
@@ -9736,7 +9732,7 @@
         <v>231</v>
       </c>
       <c r="R154" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.15">
@@ -9792,7 +9788,7 @@
         <v>231</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.15">
@@ -9848,7 +9844,7 @@
         <v>231</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.15">
@@ -9904,7 +9900,7 @@
         <v>231</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.15">
@@ -9960,7 +9956,7 @@
         <v>231</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.15">
@@ -10016,7 +10012,7 @@
         <v>231</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.15">
@@ -10072,7 +10068,7 @@
         <v>231</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.15">
@@ -10128,7 +10124,7 @@
         <v>231</v>
       </c>
       <c r="R161" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.15">
@@ -10184,7 +10180,7 @@
         <v>231</v>
       </c>
       <c r="R162" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.15">
@@ -10240,7 +10236,7 @@
         <v>231</v>
       </c>
       <c r="R163" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.15">
@@ -10296,7 +10292,7 @@
         <v>231</v>
       </c>
       <c r="R164" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3667EB-B836-492B-B537-FB4460A8D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07C176B-2884-4CD9-8D24-6A97D03D8DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -1724,7 +1724,7 @@
         <v>231</v>
       </c>
       <c r="R11" s="1">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07C176B-2884-4CD9-8D24-6A97D03D8DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C60FF9-31F7-4045-9E6E-2FB504DBE2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1712,7 +1712,7 @@
         <v>215</v>
       </c>
       <c r="N11" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="O11" s="1">
         <v>99</v>
@@ -1768,7 +1768,7 @@
         <v>215</v>
       </c>
       <c r="N12" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="O12" s="1">
         <v>4</v>
@@ -1824,7 +1824,7 @@
         <v>215</v>
       </c>
       <c r="N13" s="1">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="O13" s="1">
         <v>4</v>
@@ -1880,7 +1880,7 @@
         <v>215</v>
       </c>
       <c r="N14" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O14" s="1">
         <v>4</v>
@@ -1936,7 +1936,7 @@
         <v>215</v>
       </c>
       <c r="N15" s="1">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="O15" s="1">
         <v>4</v>
@@ -1992,7 +1992,7 @@
         <v>215</v>
       </c>
       <c r="N16" s="1">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="O16" s="1">
         <v>4</v>
@@ -2048,7 +2048,7 @@
         <v>215</v>
       </c>
       <c r="N17" s="1">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="O17" s="1">
         <v>4</v>
@@ -2104,7 +2104,7 @@
         <v>215</v>
       </c>
       <c r="N18" s="1">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="O18" s="1">
         <v>4</v>
@@ -2160,7 +2160,7 @@
         <v>215</v>
       </c>
       <c r="N19" s="1">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="O19" s="1">
         <v>4</v>
@@ -2216,7 +2216,7 @@
         <v>215</v>
       </c>
       <c r="N20" s="1">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="O20" s="1">
         <v>4</v>
@@ -2272,7 +2272,7 @@
         <v>215</v>
       </c>
       <c r="N21" s="1">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="O21" s="1">
         <v>4</v>
@@ -2328,7 +2328,7 @@
         <v>215</v>
       </c>
       <c r="N22" s="1">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="O22" s="1">
         <v>4</v>
@@ -2384,7 +2384,7 @@
         <v>215</v>
       </c>
       <c r="N23" s="1">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="O23" s="1">
         <v>4</v>
@@ -2440,7 +2440,7 @@
         <v>215</v>
       </c>
       <c r="N24" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="O24" s="1">
         <v>4</v>
@@ -2496,7 +2496,7 @@
         <v>215</v>
       </c>
       <c r="N25" s="1">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="O25" s="1">
         <v>4</v>
@@ -2552,7 +2552,7 @@
         <v>215</v>
       </c>
       <c r="N26" s="1">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="O26" s="1">
         <v>4</v>
@@ -2608,7 +2608,7 @@
         <v>215</v>
       </c>
       <c r="N27" s="1">
-        <v>2300</v>
+        <v>100</v>
       </c>
       <c r="O27" s="1">
         <v>4</v>
@@ -2664,7 +2664,7 @@
         <v>215</v>
       </c>
       <c r="N28" s="1">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="O28" s="1">
         <v>4</v>
@@ -2720,7 +2720,7 @@
         <v>215</v>
       </c>
       <c r="N29" s="1">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="O29" s="1">
         <v>4</v>
@@ -2776,7 +2776,7 @@
         <v>215</v>
       </c>
       <c r="N30" s="1">
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="O30" s="1">
         <v>4</v>
@@ -2832,7 +2832,7 @@
         <v>215</v>
       </c>
       <c r="N31" s="1">
-        <v>2700</v>
+        <v>100</v>
       </c>
       <c r="O31" s="1">
         <v>4</v>
@@ -2888,7 +2888,7 @@
         <v>215</v>
       </c>
       <c r="N32" s="1">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="O32" s="1">
         <v>4</v>
@@ -2944,7 +2944,7 @@
         <v>215</v>
       </c>
       <c r="N33" s="1">
-        <v>2900</v>
+        <v>100</v>
       </c>
       <c r="O33" s="1">
         <v>4</v>
@@ -3000,7 +3000,7 @@
         <v>215</v>
       </c>
       <c r="N34" s="1">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="O34" s="1">
         <v>4</v>
@@ -3056,7 +3056,7 @@
         <v>215</v>
       </c>
       <c r="N35" s="1">
-        <v>3100</v>
+        <v>100</v>
       </c>
       <c r="O35" s="1">
         <v>4</v>
@@ -3112,7 +3112,7 @@
         <v>215</v>
       </c>
       <c r="N36" s="1">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="O36" s="1">
         <v>4</v>
@@ -3168,7 +3168,7 @@
         <v>215</v>
       </c>
       <c r="N37" s="1">
-        <v>3300</v>
+        <v>100</v>
       </c>
       <c r="O37" s="1">
         <v>4</v>
@@ -3224,7 +3224,7 @@
         <v>215</v>
       </c>
       <c r="N38" s="1">
-        <v>3400</v>
+        <v>100</v>
       </c>
       <c r="O38" s="1">
         <v>4</v>
@@ -3280,7 +3280,7 @@
         <v>215</v>
       </c>
       <c r="N39" s="1">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="O39" s="1">
         <v>4</v>
@@ -3336,7 +3336,7 @@
         <v>215</v>
       </c>
       <c r="N40" s="1">
-        <v>3600</v>
+        <v>100</v>
       </c>
       <c r="O40" s="1">
         <v>4</v>
@@ -3392,7 +3392,7 @@
         <v>215</v>
       </c>
       <c r="N41" s="1">
-        <v>3700</v>
+        <v>100</v>
       </c>
       <c r="O41" s="1">
         <v>4</v>
@@ -3448,7 +3448,7 @@
         <v>215</v>
       </c>
       <c r="N42" s="1">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="O42" s="1">
         <v>4</v>
@@ -3504,7 +3504,7 @@
         <v>215</v>
       </c>
       <c r="N43" s="1">
-        <v>3900</v>
+        <v>100</v>
       </c>
       <c r="O43" s="1">
         <v>4</v>
@@ -3560,7 +3560,7 @@
         <v>215</v>
       </c>
       <c r="N44" s="1">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="O44" s="1">
         <v>4</v>
@@ -3616,7 +3616,7 @@
         <v>215</v>
       </c>
       <c r="N45" s="1">
-        <v>4100</v>
+        <v>100</v>
       </c>
       <c r="O45" s="1">
         <v>4</v>
@@ -3672,7 +3672,7 @@
         <v>215</v>
       </c>
       <c r="N46" s="1">
-        <v>4200</v>
+        <v>100</v>
       </c>
       <c r="O46" s="1">
         <v>4</v>
@@ -3728,7 +3728,7 @@
         <v>215</v>
       </c>
       <c r="N47" s="1">
-        <v>4300</v>
+        <v>100</v>
       </c>
       <c r="O47" s="1">
         <v>4</v>
@@ -3784,7 +3784,7 @@
         <v>215</v>
       </c>
       <c r="N48" s="1">
-        <v>4400</v>
+        <v>100</v>
       </c>
       <c r="O48" s="1">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         <v>215</v>
       </c>
       <c r="N49" s="1">
-        <v>4500</v>
+        <v>100</v>
       </c>
       <c r="O49" s="1">
         <v>4</v>
@@ -3896,7 +3896,7 @@
         <v>215</v>
       </c>
       <c r="N50" s="1">
-        <v>4600</v>
+        <v>100</v>
       </c>
       <c r="O50" s="1">
         <v>4</v>
@@ -3952,7 +3952,7 @@
         <v>215</v>
       </c>
       <c r="N51" s="1">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="O51" s="1">
         <v>4</v>
@@ -4008,7 +4008,7 @@
         <v>215</v>
       </c>
       <c r="N52" s="1">
-        <v>4800</v>
+        <v>100</v>
       </c>
       <c r="O52" s="1">
         <v>4</v>
@@ -4064,7 +4064,7 @@
         <v>215</v>
       </c>
       <c r="N53" s="1">
-        <v>4900</v>
+        <v>100</v>
       </c>
       <c r="O53" s="1">
         <v>4</v>
@@ -4120,7 +4120,7 @@
         <v>215</v>
       </c>
       <c r="N54" s="1">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="O54" s="1">
         <v>4</v>
@@ -4176,7 +4176,7 @@
         <v>215</v>
       </c>
       <c r="N55" s="1">
-        <v>5100</v>
+        <v>100</v>
       </c>
       <c r="O55" s="1">
         <v>4</v>
@@ -4232,7 +4232,7 @@
         <v>215</v>
       </c>
       <c r="N56" s="1">
-        <v>5200</v>
+        <v>100</v>
       </c>
       <c r="O56" s="1">
         <v>4</v>
@@ -4288,7 +4288,7 @@
         <v>215</v>
       </c>
       <c r="N57" s="1">
-        <v>5300</v>
+        <v>100</v>
       </c>
       <c r="O57" s="1">
         <v>4</v>
@@ -4344,7 +4344,7 @@
         <v>215</v>
       </c>
       <c r="N58" s="1">
-        <v>5400</v>
+        <v>100</v>
       </c>
       <c r="O58" s="1">
         <v>4</v>
@@ -4400,7 +4400,7 @@
         <v>215</v>
       </c>
       <c r="N59" s="1">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="O59" s="1">
         <v>4</v>
@@ -4456,7 +4456,7 @@
         <v>215</v>
       </c>
       <c r="N60" s="1">
-        <v>5600</v>
+        <v>100</v>
       </c>
       <c r="O60" s="1">
         <v>4</v>
@@ -4512,7 +4512,7 @@
         <v>215</v>
       </c>
       <c r="N61" s="1">
-        <v>5700</v>
+        <v>100</v>
       </c>
       <c r="O61" s="1">
         <v>4</v>
@@ -4568,7 +4568,7 @@
         <v>215</v>
       </c>
       <c r="N62" s="1">
-        <v>5800</v>
+        <v>100</v>
       </c>
       <c r="O62" s="1">
         <v>4</v>
@@ -4624,7 +4624,7 @@
         <v>215</v>
       </c>
       <c r="N63" s="1">
-        <v>5900</v>
+        <v>100</v>
       </c>
       <c r="O63" s="1">
         <v>4</v>
@@ -4680,7 +4680,7 @@
         <v>215</v>
       </c>
       <c r="N64" s="1">
-        <v>6000</v>
+        <v>100</v>
       </c>
       <c r="O64" s="1">
         <v>4</v>
@@ -4736,7 +4736,7 @@
         <v>215</v>
       </c>
       <c r="N65" s="1">
-        <v>6100</v>
+        <v>100</v>
       </c>
       <c r="O65" s="1">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         <v>215</v>
       </c>
       <c r="N66" s="1">
-        <v>6200</v>
+        <v>100</v>
       </c>
       <c r="O66" s="1">
         <v>4</v>
@@ -4848,7 +4848,7 @@
         <v>215</v>
       </c>
       <c r="N67" s="1">
-        <v>6300</v>
+        <v>100</v>
       </c>
       <c r="O67" s="1">
         <v>4</v>
@@ -4904,7 +4904,7 @@
         <v>215</v>
       </c>
       <c r="N68" s="1">
-        <v>6400</v>
+        <v>100</v>
       </c>
       <c r="O68" s="1">
         <v>4</v>
@@ -4960,7 +4960,7 @@
         <v>215</v>
       </c>
       <c r="N69" s="1">
-        <v>6500</v>
+        <v>100</v>
       </c>
       <c r="O69" s="1">
         <v>4</v>
@@ -5016,7 +5016,7 @@
         <v>215</v>
       </c>
       <c r="N70" s="1">
-        <v>6600</v>
+        <v>100</v>
       </c>
       <c r="O70" s="1">
         <v>4</v>
@@ -5072,7 +5072,7 @@
         <v>215</v>
       </c>
       <c r="N71" s="1">
-        <v>6700</v>
+        <v>100</v>
       </c>
       <c r="O71" s="1">
         <v>4</v>
@@ -5128,7 +5128,7 @@
         <v>215</v>
       </c>
       <c r="N72" s="1">
-        <v>6800</v>
+        <v>100</v>
       </c>
       <c r="O72" s="1">
         <v>4</v>
@@ -5184,7 +5184,7 @@
         <v>215</v>
       </c>
       <c r="N73" s="1">
-        <v>6900</v>
+        <v>100</v>
       </c>
       <c r="O73" s="1">
         <v>4</v>
@@ -5240,7 +5240,7 @@
         <v>215</v>
       </c>
       <c r="N74" s="1">
-        <v>7000</v>
+        <v>100</v>
       </c>
       <c r="O74" s="1">
         <v>4</v>
@@ -5296,7 +5296,7 @@
         <v>215</v>
       </c>
       <c r="N75" s="1">
-        <v>7100</v>
+        <v>100</v>
       </c>
       <c r="O75" s="1">
         <v>4</v>
@@ -5352,7 +5352,7 @@
         <v>215</v>
       </c>
       <c r="N76" s="1">
-        <v>7200</v>
+        <v>100</v>
       </c>
       <c r="O76" s="1">
         <v>4</v>
@@ -5408,7 +5408,7 @@
         <v>215</v>
       </c>
       <c r="N77" s="1">
-        <v>7300</v>
+        <v>100</v>
       </c>
       <c r="O77" s="1">
         <v>4</v>
@@ -5464,7 +5464,7 @@
         <v>215</v>
       </c>
       <c r="N78" s="1">
-        <v>7400</v>
+        <v>100</v>
       </c>
       <c r="O78" s="1">
         <v>4</v>
@@ -5520,7 +5520,7 @@
         <v>215</v>
       </c>
       <c r="N79" s="1">
-        <v>7500</v>
+        <v>100</v>
       </c>
       <c r="O79" s="1">
         <v>4</v>
@@ -5576,7 +5576,7 @@
         <v>215</v>
       </c>
       <c r="N80" s="1">
-        <v>7600</v>
+        <v>100</v>
       </c>
       <c r="O80" s="1">
         <v>4</v>
@@ -5632,7 +5632,7 @@
         <v>215</v>
       </c>
       <c r="N81" s="1">
-        <v>7700</v>
+        <v>100</v>
       </c>
       <c r="O81" s="1">
         <v>4</v>
@@ -5688,7 +5688,7 @@
         <v>215</v>
       </c>
       <c r="N82" s="1">
-        <v>7800</v>
+        <v>100</v>
       </c>
       <c r="O82" s="1">
         <v>4</v>
@@ -5744,7 +5744,7 @@
         <v>215</v>
       </c>
       <c r="N83" s="1">
-        <v>7900</v>
+        <v>100</v>
       </c>
       <c r="O83" s="1">
         <v>4</v>
@@ -5800,7 +5800,7 @@
         <v>215</v>
       </c>
       <c r="N84" s="1">
-        <v>8000</v>
+        <v>100</v>
       </c>
       <c r="O84" s="1">
         <v>4</v>
@@ -5856,7 +5856,7 @@
         <v>215</v>
       </c>
       <c r="N85" s="1">
-        <v>8100</v>
+        <v>100</v>
       </c>
       <c r="O85" s="1">
         <v>4</v>
@@ -5912,7 +5912,7 @@
         <v>215</v>
       </c>
       <c r="N86" s="1">
-        <v>8200</v>
+        <v>100</v>
       </c>
       <c r="O86" s="1">
         <v>4</v>
@@ -5968,7 +5968,7 @@
         <v>215</v>
       </c>
       <c r="N87" s="1">
-        <v>8300</v>
+        <v>100</v>
       </c>
       <c r="O87" s="1">
         <v>4</v>
@@ -6024,7 +6024,7 @@
         <v>215</v>
       </c>
       <c r="N88" s="1">
-        <v>8400</v>
+        <v>100</v>
       </c>
       <c r="O88" s="1">
         <v>4</v>
@@ -6080,7 +6080,7 @@
         <v>215</v>
       </c>
       <c r="N89" s="1">
-        <v>8500</v>
+        <v>100</v>
       </c>
       <c r="O89" s="1">
         <v>4</v>
@@ -6136,7 +6136,7 @@
         <v>215</v>
       </c>
       <c r="N90" s="1">
-        <v>8600</v>
+        <v>100</v>
       </c>
       <c r="O90" s="1">
         <v>4</v>
@@ -6192,7 +6192,7 @@
         <v>215</v>
       </c>
       <c r="N91" s="1">
-        <v>8700</v>
+        <v>100</v>
       </c>
       <c r="O91" s="1">
         <v>4</v>
@@ -6248,7 +6248,7 @@
         <v>215</v>
       </c>
       <c r="N92" s="1">
-        <v>8800</v>
+        <v>100</v>
       </c>
       <c r="O92" s="1">
         <v>4</v>
@@ -6304,7 +6304,7 @@
         <v>215</v>
       </c>
       <c r="N93" s="1">
-        <v>8900</v>
+        <v>100</v>
       </c>
       <c r="O93" s="1">
         <v>4</v>
@@ -6360,7 +6360,7 @@
         <v>215</v>
       </c>
       <c r="N94" s="1">
-        <v>9000</v>
+        <v>100</v>
       </c>
       <c r="O94" s="1">
         <v>4</v>
@@ -6416,7 +6416,7 @@
         <v>215</v>
       </c>
       <c r="N95" s="1">
-        <v>9100</v>
+        <v>100</v>
       </c>
       <c r="O95" s="1">
         <v>4</v>
@@ -6472,7 +6472,7 @@
         <v>215</v>
       </c>
       <c r="N96" s="1">
-        <v>9200</v>
+        <v>100</v>
       </c>
       <c r="O96" s="1">
         <v>4</v>
@@ -6528,7 +6528,7 @@
         <v>215</v>
       </c>
       <c r="N97" s="1">
-        <v>9300</v>
+        <v>100</v>
       </c>
       <c r="O97" s="1">
         <v>4</v>
@@ -6584,7 +6584,7 @@
         <v>215</v>
       </c>
       <c r="N98" s="1">
-        <v>9400</v>
+        <v>100</v>
       </c>
       <c r="O98" s="1">
         <v>4</v>
@@ -6640,7 +6640,7 @@
         <v>215</v>
       </c>
       <c r="N99" s="1">
-        <v>9500</v>
+        <v>100</v>
       </c>
       <c r="O99" s="1">
         <v>4</v>
@@ -6696,7 +6696,7 @@
         <v>215</v>
       </c>
       <c r="N100" s="1">
-        <v>9600</v>
+        <v>100</v>
       </c>
       <c r="O100" s="1">
         <v>4</v>
@@ -6752,7 +6752,7 @@
         <v>215</v>
       </c>
       <c r="N101" s="1">
-        <v>9700</v>
+        <v>100</v>
       </c>
       <c r="O101" s="1">
         <v>4</v>
@@ -6808,7 +6808,7 @@
         <v>215</v>
       </c>
       <c r="N102" s="1">
-        <v>9800</v>
+        <v>100</v>
       </c>
       <c r="O102" s="1">
         <v>4</v>
@@ -6864,7 +6864,7 @@
         <v>215</v>
       </c>
       <c r="N103" s="1">
-        <v>9900</v>
+        <v>100</v>
       </c>
       <c r="O103" s="1">
         <v>4</v>
@@ -6920,7 +6920,7 @@
         <v>215</v>
       </c>
       <c r="N104" s="1">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="O104" s="1">
         <v>4</v>
@@ -6976,7 +6976,7 @@
         <v>215</v>
       </c>
       <c r="N105" s="1">
-        <v>10100</v>
+        <v>100</v>
       </c>
       <c r="O105" s="1">
         <v>4</v>
@@ -7032,7 +7032,7 @@
         <v>215</v>
       </c>
       <c r="N106" s="1">
-        <v>10200</v>
+        <v>100</v>
       </c>
       <c r="O106" s="1">
         <v>4</v>
@@ -7088,7 +7088,7 @@
         <v>215</v>
       </c>
       <c r="N107" s="1">
-        <v>10300</v>
+        <v>100</v>
       </c>
       <c r="O107" s="1">
         <v>4</v>
@@ -7144,7 +7144,7 @@
         <v>215</v>
       </c>
       <c r="N108" s="1">
-        <v>10400</v>
+        <v>100</v>
       </c>
       <c r="O108" s="1">
         <v>4</v>
@@ -7200,7 +7200,7 @@
         <v>215</v>
       </c>
       <c r="N109" s="1">
-        <v>10500</v>
+        <v>100</v>
       </c>
       <c r="O109" s="1">
         <v>4</v>
@@ -7256,7 +7256,7 @@
         <v>215</v>
       </c>
       <c r="N110" s="1">
-        <v>10600</v>
+        <v>100</v>
       </c>
       <c r="O110" s="1">
         <v>4</v>
@@ -7312,7 +7312,7 @@
         <v>215</v>
       </c>
       <c r="N111" s="1">
-        <v>10700</v>
+        <v>100</v>
       </c>
       <c r="O111" s="1">
         <v>4</v>
@@ -7368,7 +7368,7 @@
         <v>215</v>
       </c>
       <c r="N112" s="1">
-        <v>10800</v>
+        <v>100</v>
       </c>
       <c r="O112" s="1">
         <v>4</v>
@@ -7424,7 +7424,7 @@
         <v>215</v>
       </c>
       <c r="N113" s="1">
-        <v>10900</v>
+        <v>100</v>
       </c>
       <c r="O113" s="1">
         <v>4</v>
@@ -7480,7 +7480,7 @@
         <v>215</v>
       </c>
       <c r="N114" s="1">
-        <v>11000</v>
+        <v>100</v>
       </c>
       <c r="O114" s="1">
         <v>4</v>
@@ -7536,7 +7536,7 @@
         <v>215</v>
       </c>
       <c r="N115" s="1">
-        <v>11100</v>
+        <v>100</v>
       </c>
       <c r="O115" s="1">
         <v>4</v>
@@ -7592,7 +7592,7 @@
         <v>215</v>
       </c>
       <c r="N116" s="1">
-        <v>11200</v>
+        <v>100</v>
       </c>
       <c r="O116" s="1">
         <v>4</v>
@@ -7648,7 +7648,7 @@
         <v>215</v>
       </c>
       <c r="N117" s="1">
-        <v>11300</v>
+        <v>100</v>
       </c>
       <c r="O117" s="1">
         <v>4</v>
@@ -7704,7 +7704,7 @@
         <v>215</v>
       </c>
       <c r="N118" s="1">
-        <v>11400</v>
+        <v>100</v>
       </c>
       <c r="O118" s="1">
         <v>4</v>
@@ -7760,7 +7760,7 @@
         <v>215</v>
       </c>
       <c r="N119" s="1">
-        <v>11500</v>
+        <v>100</v>
       </c>
       <c r="O119" s="1">
         <v>4</v>
@@ -7816,7 +7816,7 @@
         <v>215</v>
       </c>
       <c r="N120" s="1">
-        <v>11600</v>
+        <v>100</v>
       </c>
       <c r="O120" s="1">
         <v>4</v>
@@ -7872,7 +7872,7 @@
         <v>215</v>
       </c>
       <c r="N121" s="1">
-        <v>11700</v>
+        <v>100</v>
       </c>
       <c r="O121" s="1">
         <v>4</v>
@@ -7928,7 +7928,7 @@
         <v>215</v>
       </c>
       <c r="N122" s="1">
-        <v>11800</v>
+        <v>100</v>
       </c>
       <c r="O122" s="1">
         <v>4</v>
@@ -7984,7 +7984,7 @@
         <v>215</v>
       </c>
       <c r="N123" s="1">
-        <v>11900</v>
+        <v>100</v>
       </c>
       <c r="O123" s="1">
         <v>4</v>
@@ -8040,7 +8040,7 @@
         <v>215</v>
       </c>
       <c r="N124" s="1">
-        <v>12000</v>
+        <v>100</v>
       </c>
       <c r="O124" s="1">
         <v>4</v>
@@ -8096,7 +8096,7 @@
         <v>215</v>
       </c>
       <c r="N125" s="1">
-        <v>12100</v>
+        <v>100</v>
       </c>
       <c r="O125" s="1">
         <v>4</v>
@@ -8152,7 +8152,7 @@
         <v>215</v>
       </c>
       <c r="N126" s="1">
-        <v>12200</v>
+        <v>100</v>
       </c>
       <c r="O126" s="1">
         <v>4</v>
@@ -8208,7 +8208,7 @@
         <v>215</v>
       </c>
       <c r="N127" s="1">
-        <v>12300</v>
+        <v>100</v>
       </c>
       <c r="O127" s="1">
         <v>4</v>
@@ -8264,7 +8264,7 @@
         <v>215</v>
       </c>
       <c r="N128" s="1">
-        <v>12400</v>
+        <v>100</v>
       </c>
       <c r="O128" s="1">
         <v>4</v>
@@ -8320,7 +8320,7 @@
         <v>215</v>
       </c>
       <c r="N129" s="1">
-        <v>12500</v>
+        <v>100</v>
       </c>
       <c r="O129" s="1">
         <v>4</v>
@@ -8376,7 +8376,7 @@
         <v>215</v>
       </c>
       <c r="N130" s="1">
-        <v>12600</v>
+        <v>100</v>
       </c>
       <c r="O130" s="1">
         <v>4</v>
@@ -8432,7 +8432,7 @@
         <v>215</v>
       </c>
       <c r="N131" s="1">
-        <v>12700</v>
+        <v>100</v>
       </c>
       <c r="O131" s="1">
         <v>4</v>
@@ -8488,7 +8488,7 @@
         <v>215</v>
       </c>
       <c r="N132" s="1">
-        <v>12800</v>
+        <v>100</v>
       </c>
       <c r="O132" s="1">
         <v>4</v>
@@ -8544,7 +8544,7 @@
         <v>215</v>
       </c>
       <c r="N133" s="1">
-        <v>12900</v>
+        <v>100</v>
       </c>
       <c r="O133" s="1">
         <v>4</v>
@@ -8600,7 +8600,7 @@
         <v>215</v>
       </c>
       <c r="N134" s="1">
-        <v>13000</v>
+        <v>100</v>
       </c>
       <c r="O134" s="1">
         <v>4</v>
@@ -8656,7 +8656,7 @@
         <v>215</v>
       </c>
       <c r="N135" s="1">
-        <v>13100</v>
+        <v>100</v>
       </c>
       <c r="O135" s="1">
         <v>4</v>
@@ -8712,7 +8712,7 @@
         <v>215</v>
       </c>
       <c r="N136" s="1">
-        <v>13200</v>
+        <v>100</v>
       </c>
       <c r="O136" s="1">
         <v>4</v>
@@ -8768,7 +8768,7 @@
         <v>215</v>
       </c>
       <c r="N137" s="1">
-        <v>13300</v>
+        <v>100</v>
       </c>
       <c r="O137" s="1">
         <v>4</v>
@@ -8824,7 +8824,7 @@
         <v>215</v>
       </c>
       <c r="N138" s="1">
-        <v>13400</v>
+        <v>100</v>
       </c>
       <c r="O138" s="1">
         <v>4</v>
@@ -8880,7 +8880,7 @@
         <v>215</v>
       </c>
       <c r="N139" s="1">
-        <v>13500</v>
+        <v>100</v>
       </c>
       <c r="O139" s="1">
         <v>4</v>
@@ -8936,7 +8936,7 @@
         <v>215</v>
       </c>
       <c r="N140" s="1">
-        <v>13600</v>
+        <v>100</v>
       </c>
       <c r="O140" s="1">
         <v>4</v>
@@ -8992,7 +8992,7 @@
         <v>215</v>
       </c>
       <c r="N141" s="1">
-        <v>13700</v>
+        <v>100</v>
       </c>
       <c r="O141" s="1">
         <v>4</v>
@@ -9048,7 +9048,7 @@
         <v>215</v>
       </c>
       <c r="N142" s="1">
-        <v>13800</v>
+        <v>100</v>
       </c>
       <c r="O142" s="1">
         <v>4</v>
@@ -9104,7 +9104,7 @@
         <v>215</v>
       </c>
       <c r="N143" s="1">
-        <v>13900</v>
+        <v>100</v>
       </c>
       <c r="O143" s="1">
         <v>4</v>
@@ -9160,7 +9160,7 @@
         <v>215</v>
       </c>
       <c r="N144" s="1">
-        <v>14000</v>
+        <v>100</v>
       </c>
       <c r="O144" s="1">
         <v>4</v>
@@ -9216,7 +9216,7 @@
         <v>215</v>
       </c>
       <c r="N145" s="1">
-        <v>14100</v>
+        <v>100</v>
       </c>
       <c r="O145" s="1">
         <v>4</v>
@@ -9272,7 +9272,7 @@
         <v>215</v>
       </c>
       <c r="N146" s="1">
-        <v>14200</v>
+        <v>100</v>
       </c>
       <c r="O146" s="1">
         <v>4</v>
@@ -9328,7 +9328,7 @@
         <v>215</v>
       </c>
       <c r="N147" s="1">
-        <v>14300</v>
+        <v>100</v>
       </c>
       <c r="O147" s="1">
         <v>4</v>
@@ -9384,7 +9384,7 @@
         <v>215</v>
       </c>
       <c r="N148" s="1">
-        <v>14400</v>
+        <v>100</v>
       </c>
       <c r="O148" s="1">
         <v>4</v>
@@ -9440,7 +9440,7 @@
         <v>215</v>
       </c>
       <c r="N149" s="1">
-        <v>14500</v>
+        <v>100</v>
       </c>
       <c r="O149" s="1">
         <v>4</v>
@@ -9496,7 +9496,7 @@
         <v>215</v>
       </c>
       <c r="N150" s="1">
-        <v>14600</v>
+        <v>100</v>
       </c>
       <c r="O150" s="1">
         <v>4</v>
@@ -9552,7 +9552,7 @@
         <v>215</v>
       </c>
       <c r="N151" s="1">
-        <v>14700</v>
+        <v>100</v>
       </c>
       <c r="O151" s="1">
         <v>4</v>
@@ -9608,7 +9608,7 @@
         <v>215</v>
       </c>
       <c r="N152" s="1">
-        <v>14800</v>
+        <v>100</v>
       </c>
       <c r="O152" s="1">
         <v>4</v>
@@ -9664,7 +9664,7 @@
         <v>215</v>
       </c>
       <c r="N153" s="1">
-        <v>14900</v>
+        <v>100</v>
       </c>
       <c r="O153" s="1">
         <v>4</v>
@@ -9720,7 +9720,7 @@
         <v>215</v>
       </c>
       <c r="N154" s="1">
-        <v>15000</v>
+        <v>100</v>
       </c>
       <c r="O154" s="1">
         <v>4</v>
@@ -9776,7 +9776,7 @@
         <v>215</v>
       </c>
       <c r="N155" s="1">
-        <v>15100</v>
+        <v>100</v>
       </c>
       <c r="O155" s="1">
         <v>4</v>
@@ -9832,7 +9832,7 @@
         <v>215</v>
       </c>
       <c r="N156" s="1">
-        <v>15200</v>
+        <v>100</v>
       </c>
       <c r="O156" s="1">
         <v>4</v>
@@ -9888,7 +9888,7 @@
         <v>215</v>
       </c>
       <c r="N157" s="1">
-        <v>15300</v>
+        <v>100</v>
       </c>
       <c r="O157" s="1">
         <v>4</v>
@@ -9944,7 +9944,7 @@
         <v>215</v>
       </c>
       <c r="N158" s="1">
-        <v>15400</v>
+        <v>100</v>
       </c>
       <c r="O158" s="1">
         <v>4</v>
@@ -10000,7 +10000,7 @@
         <v>215</v>
       </c>
       <c r="N159" s="1">
-        <v>15500</v>
+        <v>100</v>
       </c>
       <c r="O159" s="1">
         <v>4</v>
@@ -10056,7 +10056,7 @@
         <v>215</v>
       </c>
       <c r="N160" s="1">
-        <v>15600</v>
+        <v>100</v>
       </c>
       <c r="O160" s="1">
         <v>4</v>
@@ -10112,7 +10112,7 @@
         <v>215</v>
       </c>
       <c r="N161" s="1">
-        <v>15700</v>
+        <v>100</v>
       </c>
       <c r="O161" s="1">
         <v>4</v>
@@ -10168,7 +10168,7 @@
         <v>215</v>
       </c>
       <c r="N162" s="1">
-        <v>15800</v>
+        <v>100</v>
       </c>
       <c r="O162" s="1">
         <v>4</v>
@@ -10224,7 +10224,7 @@
         <v>215</v>
       </c>
       <c r="N163" s="1">
-        <v>15900</v>
+        <v>100</v>
       </c>
       <c r="O163" s="1">
         <v>4</v>
@@ -10280,7 +10280,7 @@
         <v>215</v>
       </c>
       <c r="N164" s="1">
-        <v>16000</v>
+        <v>100</v>
       </c>
       <c r="O164" s="1">
         <v>4</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C60FF9-31F7-4045-9E6E-2FB504DBE2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C49A9F-15D5-49F9-996D-DD812962EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barries_v8" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="240">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1774,7 +1774,7 @@
         <v>4</v>
       </c>
       <c r="P12" s="1">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>231</v>
@@ -1805,8 +1805,8 @@
       <c r="G13" s="1">
         <v>43400002</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>202</v>
+      <c r="H13" s="1">
+        <v>0</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
@@ -1827,16 +1827,16 @@
         <v>100</v>
       </c>
       <c r="O13" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P13" s="1">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R13" s="1" t="s">
-        <v>239</v>
+      <c r="R13" s="1">
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barries_v8【迷宫-关卡信息】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C49A9F-15D5-49F9-996D-DD812962EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCB557D-1CBA-4E0C-8858-FA6450437536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="253">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -805,6 +805,58 @@
   </si>
   <si>
     <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻档位1刷怪区域：所需武力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻档位2刷怪区域：所需武力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻档位3刷怪区域：所需武力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_action1_need_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_action2_need_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_action3_need_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_S_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001:240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:0_110002:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:180_110002:550</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110001:300_110002:750</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1141,7 +1193,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R164"/>
+  <dimension ref="A1:U164"/>
   <sheetFormatPr defaultColWidth="7.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1159,15 +1211,16 @@
     <col min="15" max="16" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="7.125" style="1"/>
+    <col min="19" max="21" width="30.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="7.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1222,8 +1275,17 @@
       <c r="R2" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1278,8 +1340,17 @@
       <c r="R3" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1334,8 +1405,17 @@
       <c r="R4" s="1" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S4" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1390,8 +1470,17 @@
       <c r="R5" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S5" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1447,7 +1536,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1503,7 +1592,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1559,7 +1648,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1615,7 +1704,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1671,7 +1760,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1727,7 +1816,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1783,7 +1872,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1839,7 +1928,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1861,8 +1950,8 @@
       <c r="G14" s="1">
         <v>43400002</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>202</v>
+      <c r="H14" s="1">
+        <v>0</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
@@ -1883,19 +1972,19 @@
         <v>100</v>
       </c>
       <c r="O14" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P14" s="1">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R14" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="R14" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1917,8 +2006,8 @@
       <c r="G15" s="1">
         <v>43400002</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>202</v>
+      <c r="H15" s="1">
+        <v>0</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
@@ -1939,19 +2028,28 @@
         <v>100</v>
       </c>
       <c r="O15" s="1">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P15" s="1">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="R15" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
